--- a/artfynd/A 10361-2023 artfynd.xlsx
+++ b/artfynd/A 10361-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1625,6 +1625,142 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>69371150</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56133</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Söftenäs-Ygden, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>498250</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6271884</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-07-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-07-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Tätlövskog, björk, längs beväxt grusväg</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10361-2023 artfynd.xlsx
+++ b/artfynd/A 10361-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10361-2023 artfynd.xlsx
+++ b/artfynd/A 10361-2023 artfynd.xlsx
@@ -1358,12 +1358,7 @@
         <v>72502453</v>
       </c>
       <c r="B7" t="n">
-        <v>57508</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Dokumentation efterfrågas</t>
-        </is>
+        <v>56613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,10 +1409,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498249.8818657035</v>
+        <v>498250</v>
       </c>
       <c r="R7" t="n">
-        <v>6271884.023217525</v>
+        <v>6271884</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 10361-2023 artfynd.xlsx
+++ b/artfynd/A 10361-2023 artfynd.xlsx
@@ -1358,7 +1358,7 @@
         <v>72502453</v>
       </c>
       <c r="B7" t="n">
-        <v>56613</v>
+        <v>56615</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 10361-2023 artfynd.xlsx
+++ b/artfynd/A 10361-2023 artfynd.xlsx
@@ -1358,7 +1358,7 @@
         <v>72502453</v>
       </c>
       <c r="B7" t="n">
-        <v>56615</v>
+        <v>56617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 10361-2023 artfynd.xlsx
+++ b/artfynd/A 10361-2023 artfynd.xlsx
@@ -1358,7 +1358,7 @@
         <v>72502453</v>
       </c>
       <c r="B7" t="n">
-        <v>56617</v>
+        <v>56620</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 10361-2023 artfynd.xlsx
+++ b/artfynd/A 10361-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72502455</v>
+        <v>129456060</v>
       </c>
       <c r="B2" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,56 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söftenäs-Ygden, Sm</t>
+          <t>Ekeryd, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498249.8818657035</v>
+        <v>498215</v>
       </c>
       <c r="R2" t="n">
-        <v>6271884.023217525</v>
+        <v>6271849</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,22 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-04-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-04-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>asplåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,95 +770,74 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Tätlövskog, björk, längs beväxt grusväg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Eriksson, Lara Millon</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>72502458</v>
+        <v>120440067</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söftenäs-Ygden, Sm</t>
+          <t>Ekeryd, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498249.8818657035</v>
+        <v>498215</v>
       </c>
       <c r="R3" t="n">
-        <v>6271884.023217525</v>
+        <v>6271844</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,22 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-04-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-04-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,95 +875,78 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Tätlövskog, björk, längs beväxt grusväg</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Elin Åkelius</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Eriksson, Lara Millon</t>
+          <t>Elin Åkelius, Filip Beckman, Helene Pettersson, Love Eriksen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>72502452</v>
+        <v>129456054</v>
       </c>
       <c r="B4" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söftenäs-Ygden, Sm</t>
+          <t>Ekeryd, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498249.8818657035</v>
+        <v>498215</v>
       </c>
       <c r="R4" t="n">
-        <v>6271884.023217525</v>
+        <v>6271849</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1036,22 +970,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-04-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-04-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på fyra olika asplågor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1060,38 +989,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Tätlövskog, björk, längs beväxt grusväg</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Eriksson, Lara Millon</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>72502451</v>
+        <v>129456065</v>
       </c>
       <c r="B5" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92525</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,56 +1019,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206002</v>
+        <v>1265</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Stor tratticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Picipes badius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Zmitr. &amp; Kovalenko</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söftenäs-Ygden, Sm</t>
+          <t>Ekeryd, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498249.8818657035</v>
+        <v>498215</v>
       </c>
       <c r="R5" t="n">
-        <v>6271884.023217525</v>
+        <v>6271849</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1172,22 +1084,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-04-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-04-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>asplåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1196,38 +1103,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Tätlövskog, björk, längs beväxt grusväg</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Eriksson, Lara Millon</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>72502457</v>
+        <v>129456076</v>
       </c>
       <c r="B6" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,56 +1133,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100092</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söftenäs-Ygden, Sm</t>
+          <t>Ekeryd, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498249.8818657035</v>
+        <v>498215</v>
       </c>
       <c r="R6" t="n">
-        <v>6271884.023217525</v>
+        <v>6271849</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1308,22 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-04-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-04-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1332,33 +1205,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Tätlövskog, björk, längs beväxt grusväg</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Eriksson, Lara Millon</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>72502453</v>
+        <v>129456094</v>
       </c>
       <c r="B7" t="n">
-        <v>56620</v>
+        <v>75300</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,56 +1235,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206000</v>
+        <v>6428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gråskimlig fladdermus</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Vespertilio murinus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söftenäs-Ygden, Sm</t>
+          <t>Ekeryd, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498250</v>
+        <v>498215</v>
       </c>
       <c r="R7" t="n">
-        <v>6271884</v>
+        <v>6271849</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1439,22 +1292,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-04-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-04-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>på ek</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1463,23 +1311,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Tätlövskog, björk, längs beväxt grusväg</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexander Eriksson, Lara Millon</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1489,12 +1333,7 @@
         <v>69371150</v>
       </c>
       <c r="B8" t="n">
-        <v>56162</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56814</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1619,6 +1458,895 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>72502457</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56830</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Söftenäs-Ygden, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>498250</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6271884</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-04-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Tätlövskog, björk, längs beväxt grusväg</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson, Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129456101</v>
+      </c>
+      <c r="B10" t="n">
+        <v>30288</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>200985</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blanksvart trämyra</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lasius fuliginosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Latreille, 1798)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ekeryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>498215</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6271849</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>72502458</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Söftenäs-Ygden, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>498250</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6271884</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2017-04-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Tätlövskog, björk, längs beväxt grusväg</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson, Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>72502452</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Söftenäs-Ygden, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>498250</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6271884</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2017-04-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Tätlövskog, björk, längs beväxt grusväg</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson, Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>72502455</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Söftenäs-Ygden, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>498250</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6271884</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2017-04-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Tätlövskog, björk, längs beväxt grusväg</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson, Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>72502453</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56840</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Söftenäs-Ygden, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>498250</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6271884</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2017-04-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Tätlövskog, björk, längs beväxt grusväg</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson, Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>72502451</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Söftenäs-Ygden, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>498250</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6271884</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2017-04-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Tätlövskog, björk, längs beväxt grusväg</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson, Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
